--- a/downloads/kerala.xlsx
+++ b/downloads/kerala.xlsx
@@ -860,19 +860,19 @@
         <v>14053</v>
       </c>
       <c r="I2" t="n">
-        <v>6.22</v>
+        <v>6.2244</v>
       </c>
       <c r="J2" t="n">
         <v>-4340</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.92</v>
+        <v>-1.9223</v>
       </c>
       <c r="L2" t="n">
-        <v>49.92</v>
+        <v>49.9192</v>
       </c>
       <c r="M2" t="n">
-        <v>59.16</v>
+        <v>59.1617</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>187801</v>
       </c>
       <c r="R2" t="n">
-        <v>81.61</v>
+        <v>81.6125</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
         <v>14803</v>
       </c>
       <c r="I3" t="n">
-        <v>7.19</v>
+        <v>7.1941</v>
       </c>
       <c r="J3" t="n">
         <v>-5156</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.51</v>
+        <v>-2.5057</v>
       </c>
       <c r="L3" t="n">
-        <v>50.28</v>
+        <v>50.2777</v>
       </c>
       <c r="M3" t="n">
-        <v>58.45</v>
+        <v>58.4476</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>169203</v>
       </c>
       <c r="R3" t="n">
-        <v>80.22</v>
+        <v>80.22029999999999</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1008,19 +1008,19 @@
         <v>8799</v>
       </c>
       <c r="I4" t="n">
-        <v>4.01</v>
+        <v>4.0132</v>
       </c>
       <c r="J4" t="n">
         <v>-9259</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.22</v>
+        <v>-4.223</v>
       </c>
       <c r="L4" t="n">
-        <v>51.18</v>
+        <v>51.1756</v>
       </c>
       <c r="M4" t="n">
-        <v>59.85</v>
+        <v>59.8477</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>180816</v>
       </c>
       <c r="R4" t="n">
-        <v>79.13</v>
+        <v>79.1276</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>10279</v>
       </c>
       <c r="I5" t="n">
-        <v>4.65</v>
+        <v>4.647</v>
       </c>
       <c r="J5" t="n">
         <v>-2783</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.26</v>
+        <v>-1.2582</v>
       </c>
       <c r="L5" t="n">
-        <v>51.99</v>
+        <v>51.9894</v>
       </c>
       <c r="M5" t="n">
         <v>56.63</v>
@@ -1113,7 +1113,7 @@
         <v>175777</v>
       </c>
       <c r="R5" t="n">
-        <v>78.48</v>
+        <v>78.4789</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1156,19 +1156,19 @@
         <v>7355</v>
       </c>
       <c r="I6" t="n">
-        <v>3.59</v>
+        <v>3.594</v>
       </c>
       <c r="J6" t="n">
         <v>-5446</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.66</v>
+        <v>-2.6612</v>
       </c>
       <c r="L6" t="n">
-        <v>52.37</v>
+        <v>52.3656</v>
       </c>
       <c r="M6" t="n">
-        <v>57.85</v>
+        <v>57.8518</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>170904</v>
       </c>
       <c r="R6" t="n">
-        <v>81.34999999999999</v>
+        <v>81.348</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1230,19 +1230,19 @@
         <v>7937</v>
       </c>
       <c r="I7" t="n">
-        <v>4.27</v>
+        <v>4.2651</v>
       </c>
       <c r="J7" t="n">
         <v>-2842</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.53</v>
+        <v>-1.5272</v>
       </c>
       <c r="L7" t="n">
-        <v>52.44</v>
+        <v>52.441</v>
       </c>
       <c r="M7" t="n">
-        <v>51.35</v>
+        <v>51.3544</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>155970</v>
       </c>
       <c r="R7" t="n">
-        <v>82.55</v>
+        <v>82.5522</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1304,19 +1304,19 @@
         <v>8111</v>
       </c>
       <c r="I8" t="n">
-        <v>4.24</v>
+        <v>4.2377</v>
       </c>
       <c r="J8" t="n">
         <v>-12396</v>
       </c>
       <c r="K8" t="n">
-        <v>-6.48</v>
+        <v>-6.4765</v>
       </c>
       <c r="L8" t="n">
-        <v>54.05</v>
+        <v>54.0455</v>
       </c>
       <c r="M8" t="n">
-        <v>56.08</v>
+        <v>56.0843</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>159867</v>
       </c>
       <c r="R8" t="n">
-        <v>78.44</v>
+        <v>78.44459999999999</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1378,19 +1378,19 @@
         <v>7553</v>
       </c>
       <c r="I9" t="n">
-        <v>3.42</v>
+        <v>3.4178</v>
       </c>
       <c r="J9" t="n">
         <v>-11293</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.11</v>
+        <v>-5.1103</v>
       </c>
       <c r="L9" t="n">
-        <v>52.85</v>
+        <v>52.8461</v>
       </c>
       <c r="M9" t="n">
-        <v>53.86</v>
+        <v>53.8594</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>192175</v>
       </c>
       <c r="R9" t="n">
-        <v>82.73</v>
+        <v>82.7342</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1452,19 +1452,19 @@
         <v>10345</v>
       </c>
       <c r="I10" t="n">
-        <v>5.24</v>
+        <v>5.2412</v>
       </c>
       <c r="J10" t="n">
         <v>-1949</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.99</v>
+        <v>-0.9875</v>
       </c>
       <c r="L10" t="n">
-        <v>50.74</v>
+        <v>50.7394</v>
       </c>
       <c r="M10" t="n">
-        <v>54.17</v>
+        <v>54.1711</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>151645</v>
       </c>
       <c r="R10" t="n">
-        <v>76.08</v>
+        <v>76.0789</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1526,19 +1526,19 @@
         <v>11178</v>
       </c>
       <c r="I11" t="n">
-        <v>6.04</v>
+        <v>6.0427</v>
       </c>
       <c r="J11" t="n">
         <v>-3267</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.77</v>
+        <v>-1.7661</v>
       </c>
       <c r="L11" t="n">
-        <v>53.37</v>
+        <v>53.3714</v>
       </c>
       <c r="M11" t="n">
-        <v>52.55</v>
+        <v>52.5497</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>148412</v>
       </c>
       <c r="R11" t="n">
-        <v>78.84</v>
+        <v>78.8377</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1600,19 +1600,19 @@
         <v>11468</v>
       </c>
       <c r="I12" t="n">
-        <v>6.43</v>
+        <v>6.4309</v>
       </c>
       <c r="J12" t="n">
         <v>-4355</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.44</v>
+        <v>-2.4421</v>
       </c>
       <c r="L12" t="n">
-        <v>53.11</v>
+        <v>53.1137</v>
       </c>
       <c r="M12" t="n">
-        <v>52.01</v>
+        <v>52.0056</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1674,19 +1674,19 @@
         <v>7596</v>
       </c>
       <c r="I13" t="n">
-        <v>3.82</v>
+        <v>3.8206</v>
       </c>
       <c r="J13" t="n">
         <v>-7181</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.61</v>
+        <v>-3.6118</v>
       </c>
       <c r="L13" t="n">
-        <v>53.38</v>
+        <v>53.3832</v>
       </c>
       <c r="M13" t="n">
-        <v>54.21</v>
+        <v>54.2127</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>171659</v>
       </c>
       <c r="R13" t="n">
-        <v>83.33</v>
+        <v>83.3296</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1748,19 +1748,19 @@
         <v>10285</v>
       </c>
       <c r="I14" t="n">
-        <v>5.76</v>
+        <v>5.7611</v>
       </c>
       <c r="J14" t="n">
         <v>-7316</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.1</v>
+        <v>-4.098</v>
       </c>
       <c r="L14" t="n">
-        <v>53.33</v>
+        <v>53.3264</v>
       </c>
       <c r="M14" t="n">
-        <v>56.28</v>
+        <v>56.2761</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1822,19 +1822,19 @@
         <v>10119</v>
       </c>
       <c r="I15" t="n">
-        <v>5.02</v>
+        <v>5.0176</v>
       </c>
       <c r="J15" t="n">
         <v>-4100</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.03</v>
+        <v>-2.033</v>
       </c>
       <c r="L15" t="n">
-        <v>52.17</v>
+        <v>52.1731</v>
       </c>
       <c r="M15" t="n">
-        <v>55.45</v>
+        <v>55.4501</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>164202</v>
       </c>
       <c r="R15" t="n">
-        <v>79.8</v>
+        <v>79.7984</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1896,19 +1896,19 @@
         <v>6399</v>
       </c>
       <c r="I16" t="n">
-        <v>3.29</v>
+        <v>3.2877</v>
       </c>
       <c r="J16" t="n">
         <v>-7086</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.64</v>
+        <v>-3.6407</v>
       </c>
       <c r="L16" t="n">
-        <v>52.38</v>
+        <v>52.3837</v>
       </c>
       <c r="M16" t="n">
-        <v>57.21</v>
+        <v>57.2121</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>169858</v>
       </c>
       <c r="R16" t="n">
-        <v>84.20999999999999</v>
+        <v>84.20529999999999</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1970,19 +1970,19 @@
         <v>7760</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>4.2981</v>
       </c>
       <c r="J17" t="n">
         <v>-1840</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.02</v>
+        <v>-1.0191</v>
       </c>
       <c r="L17" t="n">
-        <v>51.07</v>
+        <v>51.0657</v>
       </c>
       <c r="M17" t="n">
-        <v>55.21</v>
+        <v>55.2062</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>147244</v>
       </c>
       <c r="R17" t="n">
-        <v>80.73</v>
+        <v>80.733</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2044,19 +2044,19 @@
         <v>10224</v>
       </c>
       <c r="I18" t="n">
-        <v>5.03</v>
+        <v>5.0319</v>
       </c>
       <c r="J18" t="n">
         <v>-2231</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1</v>
+        <v>-1.098</v>
       </c>
       <c r="L18" t="n">
-        <v>50.71</v>
+        <v>50.7082</v>
       </c>
       <c r="M18" t="n">
-        <v>52.95</v>
+        <v>52.9538</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>165006</v>
       </c>
       <c r="R18" t="n">
-        <v>80.33</v>
+        <v>80.32810000000001</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2118,19 +2118,19 @@
         <v>13179</v>
       </c>
       <c r="I19" t="n">
-        <v>5.79</v>
+        <v>5.7853</v>
       </c>
       <c r="J19" t="n">
         <v>2472</v>
       </c>
       <c r="K19" t="n">
-        <v>1.09</v>
+        <v>1.0852</v>
       </c>
       <c r="L19" t="n">
-        <v>51.36</v>
+        <v>51.3553</v>
       </c>
       <c r="M19" t="n">
-        <v>52.29</v>
+        <v>52.2877</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>176938</v>
       </c>
       <c r="R19" t="n">
-        <v>78.52</v>
+        <v>78.5243</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2192,19 +2192,19 @@
         <v>14310</v>
       </c>
       <c r="I20" t="n">
-        <v>6.78</v>
+        <v>6.7751</v>
       </c>
       <c r="J20" t="n">
         <v>-1666</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.79</v>
+        <v>-0.7887999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>51.37</v>
+        <v>51.3699</v>
       </c>
       <c r="M20" t="n">
-        <v>54.27</v>
+        <v>54.2697</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>173441</v>
       </c>
       <c r="R20" t="n">
-        <v>81.47</v>
+        <v>81.47320000000001</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2266,19 +2266,19 @@
         <v>10988</v>
       </c>
       <c r="I21" t="n">
-        <v>6.23</v>
+        <v>6.2322</v>
       </c>
       <c r="J21" t="n">
         <v>-523</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3</v>
+        <v>-0.2966</v>
       </c>
       <c r="L21" t="n">
-        <v>52.3</v>
+        <v>52.2985</v>
       </c>
       <c r="M21" t="n">
-        <v>56.58</v>
+        <v>56.5799</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>143179</v>
       </c>
       <c r="R21" t="n">
-        <v>80.97</v>
+        <v>80.9689</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2340,19 +2340,19 @@
         <v>12484</v>
       </c>
       <c r="I22" t="n">
-        <v>5.83</v>
+        <v>5.8273</v>
       </c>
       <c r="J22" t="n">
         <v>-1707</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8</v>
+        <v>-0.7968</v>
       </c>
       <c r="L22" t="n">
-        <v>51.53</v>
+        <v>51.5308</v>
       </c>
       <c r="M22" t="n">
-        <v>54.04</v>
+        <v>54.0372</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>178106</v>
       </c>
       <c r="R22" t="n">
-        <v>82.48</v>
+        <v>82.4794</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2414,19 +2414,19 @@
         <v>13382</v>
       </c>
       <c r="I23" t="n">
-        <v>5.81</v>
+        <v>5.8136</v>
       </c>
       <c r="J23" t="n">
         <v>-3507</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.52</v>
+        <v>-1.5236</v>
       </c>
       <c r="L23" t="n">
-        <v>51.14</v>
+        <v>51.1367</v>
       </c>
       <c r="M23" t="n">
-        <v>55.33</v>
+        <v>55.3281</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>188712</v>
       </c>
       <c r="R23" t="n">
-        <v>80.75</v>
+        <v>80.7531</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2488,19 +2488,19 @@
         <v>14896</v>
       </c>
       <c r="I24" t="n">
-        <v>6.97</v>
+        <v>6.9749</v>
       </c>
       <c r="J24" t="n">
         <v>311</v>
       </c>
       <c r="K24" t="n">
-        <v>0.15</v>
+        <v>0.1456</v>
       </c>
       <c r="L24" t="n">
-        <v>52.51</v>
+        <v>52.5086</v>
       </c>
       <c r="M24" t="n">
-        <v>58.88</v>
+        <v>58.8816</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>172425</v>
       </c>
       <c r="R24" t="n">
-        <v>80.84999999999999</v>
+        <v>80.85429999999999</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2562,19 +2562,19 @@
         <v>12128</v>
       </c>
       <c r="I25" t="n">
-        <v>5.88</v>
+        <v>5.8776</v>
       </c>
       <c r="J25" t="n">
         <v>374</v>
       </c>
       <c r="K25" t="n">
-        <v>0.18</v>
+        <v>0.1813</v>
       </c>
       <c r="L25" t="n">
-        <v>51.64</v>
+        <v>51.6443</v>
       </c>
       <c r="M25" t="n">
-        <v>57.12</v>
+        <v>57.1158</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>172086</v>
       </c>
       <c r="R25" t="n">
-        <v>83.55</v>
+        <v>83.5491</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2636,19 +2636,19 @@
         <v>17336</v>
       </c>
       <c r="I26" t="n">
-        <v>7.5</v>
+        <v>7.4963</v>
       </c>
       <c r="J26" t="n">
         <v>2573</v>
       </c>
       <c r="K26" t="n">
-        <v>1.11</v>
+        <v>1.1126</v>
       </c>
       <c r="L26" t="n">
-        <v>51.97</v>
+        <v>51.9662</v>
       </c>
       <c r="M26" t="n">
-        <v>57.57</v>
+        <v>57.5738</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>191315</v>
       </c>
       <c r="R26" t="n">
-        <v>83.66</v>
+        <v>83.65730000000001</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2710,19 +2710,19 @@
         <v>11831</v>
       </c>
       <c r="I27" t="n">
-        <v>5.65</v>
+        <v>5.6548</v>
       </c>
       <c r="J27" t="n">
         <v>-1884</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.9</v>
+        <v>-0.9005</v>
       </c>
       <c r="L27" t="n">
-        <v>52.21</v>
+        <v>52.208</v>
       </c>
       <c r="M27" t="n">
-        <v>58.92</v>
+        <v>58.9215</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>177765</v>
       </c>
       <c r="R27" t="n">
-        <v>84.20999999999999</v>
+        <v>84.2069</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2784,19 +2784,19 @@
         <v>23289</v>
       </c>
       <c r="I28" t="n">
-        <v>12.63</v>
+        <v>12.6321</v>
       </c>
       <c r="J28" t="n">
         <v>11159</v>
       </c>
       <c r="K28" t="n">
-        <v>6.05</v>
+        <v>6.0527</v>
       </c>
       <c r="L28" t="n">
-        <v>52.97</v>
+        <v>52.9724</v>
       </c>
       <c r="M28" t="n">
-        <v>55.67</v>
+        <v>55.6701</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>141535</v>
       </c>
       <c r="R28" t="n">
-        <v>81.72</v>
+        <v>81.7153</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -2858,19 +2858,19 @@
         <v>17738</v>
       </c>
       <c r="I29" t="n">
-        <v>11.11</v>
+        <v>11.1118</v>
       </c>
       <c r="J29" t="n">
         <v>3660</v>
       </c>
       <c r="K29" t="n">
-        <v>2.29</v>
+        <v>2.2928</v>
       </c>
       <c r="L29" t="n">
-        <v>51.67</v>
+        <v>51.6682</v>
       </c>
       <c r="M29" t="n">
-        <v>54.4</v>
+        <v>54.3973</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>127866</v>
       </c>
       <c r="R29" t="n">
-        <v>81.98</v>
+        <v>81.98009999999999</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -2932,19 +2932,19 @@
         <v>16836</v>
       </c>
       <c r="I30" t="n">
-        <v>7.82</v>
+        <v>7.816</v>
       </c>
       <c r="J30" t="n">
         <v>-3155</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.46</v>
+        <v>-1.4647</v>
       </c>
       <c r="L30" t="n">
-        <v>51.33</v>
+        <v>51.3345</v>
       </c>
       <c r="M30" t="n">
-        <v>56.79</v>
+        <v>56.795</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>185150</v>
       </c>
       <c r="R30" t="n">
-        <v>84.70999999999999</v>
+        <v>84.7144</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3006,19 +3006,19 @@
         <v>15646</v>
       </c>
       <c r="I31" t="n">
-        <v>6.49</v>
+        <v>6.4893</v>
       </c>
       <c r="J31" t="n">
         <v>-875</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.36</v>
+        <v>-0.3629</v>
       </c>
       <c r="L31" t="n">
-        <v>51.42</v>
+        <v>51.4241</v>
       </c>
       <c r="M31" t="n">
-        <v>57.61</v>
+        <v>57.6122</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>208949</v>
       </c>
       <c r="R31" t="n">
-        <v>86.34999999999999</v>
+        <v>86.3497</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3080,19 +3080,19 @@
         <v>7915</v>
       </c>
       <c r="I32" t="n">
-        <v>4.17</v>
+        <v>4.1676</v>
       </c>
       <c r="J32" t="n">
         <v>-11751</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.19</v>
+        <v>-6.1874</v>
       </c>
       <c r="L32" t="n">
-        <v>50.07</v>
+        <v>50.0692</v>
       </c>
       <c r="M32" t="n">
-        <v>55.05</v>
+        <v>55.0474</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>165988</v>
       </c>
       <c r="R32" t="n">
-        <v>82.31</v>
+        <v>82.30759999999999</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3154,19 +3154,19 @@
         <v>10424</v>
       </c>
       <c r="I33" t="n">
-        <v>5.6</v>
+        <v>5.6036</v>
       </c>
       <c r="J33" t="n">
         <v>-5931</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.19</v>
+        <v>-3.1883</v>
       </c>
       <c r="L33" t="n">
-        <v>50.55</v>
+        <v>50.5518</v>
       </c>
       <c r="M33" t="n">
-        <v>56.12</v>
+        <v>56.1205</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>156680</v>
       </c>
       <c r="R33" t="n">
-        <v>81.62</v>
+        <v>81.6237</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3228,19 +3228,19 @@
         <v>7975</v>
       </c>
       <c r="I34" t="n">
-        <v>3.72</v>
+        <v>3.7233</v>
       </c>
       <c r="J34" t="n">
         <v>-15181</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.09</v>
+        <v>-7.0877</v>
       </c>
       <c r="L34" t="n">
-        <v>49.22</v>
+        <v>49.2201</v>
       </c>
       <c r="M34" t="n">
-        <v>61.38</v>
+        <v>61.3793</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>191625</v>
       </c>
       <c r="R34" t="n">
-        <v>83.54000000000001</v>
+        <v>83.5441</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3302,19 +3302,19 @@
         <v>7034</v>
       </c>
       <c r="I35" t="n">
-        <v>3.78</v>
+        <v>3.7821</v>
       </c>
       <c r="J35" t="n">
         <v>-13575</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.3</v>
+        <v>-7.2991</v>
       </c>
       <c r="L35" t="n">
-        <v>49.31</v>
+        <v>49.3056</v>
       </c>
       <c r="M35" t="n">
-        <v>61.8</v>
+        <v>61.7998</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>168681</v>
       </c>
       <c r="R35" t="n">
-        <v>84.53</v>
+        <v>84.5282</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3376,19 +3376,19 @@
         <v>5706</v>
       </c>
       <c r="I36" t="n">
-        <v>2.51</v>
+        <v>2.5098</v>
       </c>
       <c r="J36" t="n">
         <v>-9228</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.06</v>
+        <v>-4.059</v>
       </c>
       <c r="L36" t="n">
-        <v>51.12</v>
+        <v>51.1155</v>
       </c>
       <c r="M36" t="n">
-        <v>63.11</v>
+        <v>63.109</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>189595</v>
       </c>
       <c r="R36" t="n">
-        <v>80.14</v>
+        <v>80.1413</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3450,19 +3450,19 @@
         <v>12134</v>
       </c>
       <c r="I37" t="n">
-        <v>5.16</v>
+        <v>5.1615</v>
       </c>
       <c r="J37" t="n">
         <v>-12099</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.15</v>
+        <v>-5.1466</v>
       </c>
       <c r="L37" t="n">
-        <v>50.72</v>
+        <v>50.7221</v>
       </c>
       <c r="M37" t="n">
-        <v>58.27</v>
+        <v>58.2743</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>203168</v>
       </c>
       <c r="R37" t="n">
-        <v>82.19</v>
+        <v>82.193</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3524,19 +3524,19 @@
         <v>11593</v>
       </c>
       <c r="I38" t="n">
-        <v>5.41</v>
+        <v>5.4108</v>
       </c>
       <c r="J38" t="n">
         <v>-13507</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.3</v>
+        <v>-6.3042</v>
       </c>
       <c r="L38" t="n">
-        <v>50.07</v>
+        <v>50.0721</v>
       </c>
       <c r="M38" t="n">
-        <v>62.25</v>
+        <v>62.2531</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>190019</v>
       </c>
       <c r="R38" t="n">
-        <v>83.43000000000001</v>
+        <v>83.4288</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3598,19 +3598,19 @@
         <v>10097</v>
       </c>
       <c r="I39" t="n">
-        <v>4.65</v>
+        <v>4.6501</v>
       </c>
       <c r="J39" t="n">
         <v>-12391</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.71</v>
+        <v>-5.7066</v>
       </c>
       <c r="L39" t="n">
-        <v>50.8</v>
+        <v>50.7981</v>
       </c>
       <c r="M39" t="n">
-        <v>62.12</v>
+        <v>62.1175</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>186088</v>
       </c>
       <c r="R39" t="n">
-        <v>81.08</v>
+        <v>81.0753</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -3672,19 +3672,19 @@
         <v>9425</v>
       </c>
       <c r="I40" t="n">
-        <v>4.34</v>
+        <v>4.3389</v>
       </c>
       <c r="J40" t="n">
         <v>-13617</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.27</v>
+        <v>-6.2687</v>
       </c>
       <c r="L40" t="n">
-        <v>50.16</v>
+        <v>50.1572</v>
       </c>
       <c r="M40" t="n">
-        <v>62.65</v>
+        <v>62.6525</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>187686</v>
       </c>
       <c r="R40" t="n">
-        <v>81.31</v>
+        <v>81.3064</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -3746,19 +3746,19 @@
         <v>8985</v>
       </c>
       <c r="I41" t="n">
-        <v>4.06</v>
+        <v>4.0602</v>
       </c>
       <c r="J41" t="n">
         <v>-16783</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.58</v>
+        <v>-7.5839</v>
       </c>
       <c r="L41" t="n">
-        <v>49.17</v>
+        <v>49.1679</v>
       </c>
       <c r="M41" t="n">
-        <v>60.16</v>
+        <v>60.1558</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>196885</v>
       </c>
       <c r="R41" t="n">
-        <v>82.7</v>
+        <v>82.697</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -3826,13 +3826,13 @@
         <v>-20818</v>
       </c>
       <c r="K42" t="n">
-        <v>-10.91</v>
+        <v>-10.9102</v>
       </c>
       <c r="L42" t="n">
-        <v>48.18</v>
+        <v>48.1778</v>
       </c>
       <c r="M42" t="n">
-        <v>59.34</v>
+        <v>59.3365</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>170289</v>
       </c>
       <c r="R42" t="n">
-        <v>80.47</v>
+        <v>80.4654</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -3894,19 +3894,19 @@
         <v>7738</v>
       </c>
       <c r="I43" t="n">
-        <v>3.76</v>
+        <v>3.7582</v>
       </c>
       <c r="J43" t="n">
         <v>-15141</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.35</v>
+        <v>-7.3537</v>
       </c>
       <c r="L43" t="n">
-        <v>49.29</v>
+        <v>49.2897</v>
       </c>
       <c r="M43" t="n">
-        <v>57.82</v>
+        <v>57.8186</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>181022</v>
       </c>
       <c r="R43" t="n">
-        <v>81.90000000000001</v>
+        <v>81.89709999999999</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -3974,13 +3974,13 @@
         <v>-17398</v>
       </c>
       <c r="K44" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.470499999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>49.13</v>
+        <v>49.1314</v>
       </c>
       <c r="M44" t="n">
-        <v>58.73</v>
+        <v>58.726</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>176214</v>
       </c>
       <c r="R44" t="n">
-        <v>79.09</v>
+        <v>79.09350000000001</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4042,19 +4042,19 @@
         <v>10574</v>
       </c>
       <c r="I45" t="n">
-        <v>5.32</v>
+        <v>5.3213</v>
       </c>
       <c r="J45" t="n">
         <v>-15392</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.75</v>
+        <v>-7.746</v>
       </c>
       <c r="L45" t="n">
-        <v>49.77</v>
+        <v>49.7708</v>
       </c>
       <c r="M45" t="n">
-        <v>59.08</v>
+        <v>59.0789</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>172324</v>
       </c>
       <c r="R45" t="n">
-        <v>80.48999999999999</v>
+        <v>80.4872</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4116,19 +4116,19 @@
         <v>12281</v>
       </c>
       <c r="I46" t="n">
-        <v>5.26</v>
+        <v>5.2575</v>
       </c>
       <c r="J46" t="n">
         <v>-21850</v>
       </c>
       <c r="K46" t="n">
-        <v>-9.35</v>
+        <v>-9.353999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>50.61</v>
+        <v>50.6137</v>
       </c>
       <c r="M46" t="n">
-        <v>58.9</v>
+        <v>58.904</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>198509</v>
       </c>
       <c r="R46" t="n">
-        <v>77.70999999999999</v>
+        <v>77.7123</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4190,19 +4190,19 @@
         <v>11023</v>
       </c>
       <c r="I47" t="n">
-        <v>4.93</v>
+        <v>4.9305</v>
       </c>
       <c r="J47" t="n">
         <v>-19446</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.698</v>
       </c>
       <c r="L47" t="n">
-        <v>49.57</v>
+        <v>49.5697</v>
       </c>
       <c r="M47" t="n">
-        <v>56.99</v>
+        <v>56.9899</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>191211</v>
       </c>
       <c r="R47" t="n">
-        <v>78.68000000000001</v>
+        <v>78.6831</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4264,19 +4264,19 @@
         <v>14125</v>
       </c>
       <c r="I48" t="n">
-        <v>6.92</v>
+        <v>6.9239</v>
       </c>
       <c r="J48" t="n">
         <v>-4772</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.34</v>
+        <v>-2.3392</v>
       </c>
       <c r="L48" t="n">
         <v>50.9</v>
       </c>
       <c r="M48" t="n">
-        <v>59.97</v>
+        <v>59.9717</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>163886</v>
       </c>
       <c r="R48" t="n">
-        <v>78.5</v>
+        <v>78.49850000000001</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4338,19 +4338,19 @@
         <v>18031</v>
       </c>
       <c r="I49" t="n">
-        <v>8.710000000000001</v>
+        <v>8.7067</v>
       </c>
       <c r="J49" t="n">
         <v>-9435</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.56</v>
+        <v>-4.5559</v>
       </c>
       <c r="L49" t="n">
-        <v>51.61</v>
+        <v>51.6084</v>
       </c>
       <c r="M49" t="n">
-        <v>59.04</v>
+        <v>59.0428</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>161973</v>
       </c>
       <c r="R49" t="n">
-        <v>74.8</v>
+        <v>74.8043</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4412,19 +4412,19 @@
         <v>11801</v>
       </c>
       <c r="I50" t="n">
-        <v>5.93</v>
+        <v>5.9307</v>
       </c>
       <c r="J50" t="n">
         <v>-4717</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.37</v>
+        <v>-2.3706</v>
       </c>
       <c r="L50" t="n">
-        <v>51.27</v>
+        <v>51.2722</v>
       </c>
       <c r="M50" t="n">
-        <v>58.28</v>
+        <v>58.2832</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4486,19 +4486,19 @@
         <v>9630</v>
       </c>
       <c r="I51" t="n">
-        <v>4.76</v>
+        <v>4.7628</v>
       </c>
       <c r="J51" t="n">
         <v>-8596</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.25</v>
+        <v>-4.2514</v>
       </c>
       <c r="L51" t="n">
-        <v>50.56</v>
+        <v>50.5633</v>
       </c>
       <c r="M51" t="n">
-        <v>57.66</v>
+        <v>57.6636</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>169436</v>
       </c>
       <c r="R51" t="n">
-        <v>80.38</v>
+        <v>80.3814</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         <v>9548</v>
       </c>
       <c r="I52" t="n">
-        <v>4.86</v>
+        <v>4.8621</v>
       </c>
       <c r="J52" t="n">
         <v>-3245</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.65</v>
+        <v>-1.6525</v>
       </c>
       <c r="L52" t="n">
-        <v>51.39</v>
+        <v>51.3905</v>
       </c>
       <c r="M52" t="n">
-        <v>57.1</v>
+        <v>57.101</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>160123</v>
       </c>
       <c r="R52" t="n">
-        <v>80.20999999999999</v>
+        <v>80.2139</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -4634,19 +4634,19 @@
         <v>13170</v>
       </c>
       <c r="I53" t="n">
-        <v>6.23</v>
+        <v>6.2307</v>
       </c>
       <c r="J53" t="n">
         <v>1747</v>
       </c>
       <c r="K53" t="n">
-        <v>0.83</v>
+        <v>0.8265</v>
       </c>
       <c r="L53" t="n">
-        <v>51.67</v>
+        <v>51.6738</v>
       </c>
       <c r="M53" t="n">
-        <v>56.95</v>
+        <v>56.9476</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>170104</v>
       </c>
       <c r="R53" t="n">
-        <v>81.15000000000001</v>
+        <v>81.146</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -4708,19 +4708,19 @@
         <v>11756</v>
       </c>
       <c r="I54" t="n">
-        <v>6.4</v>
+        <v>6.3991</v>
       </c>
       <c r="J54" t="n">
         <v>1111</v>
       </c>
       <c r="K54" t="n">
-        <v>0.6</v>
+        <v>0.6047</v>
       </c>
       <c r="L54" t="n">
-        <v>50.97</v>
+        <v>50.9667</v>
       </c>
       <c r="M54" t="n">
-        <v>56.6</v>
+        <v>56.6009</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>148655</v>
       </c>
       <c r="R54" t="n">
-        <v>81.41</v>
+        <v>81.4088</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -4782,19 +4782,19 @@
         <v>11699</v>
       </c>
       <c r="I55" t="n">
-        <v>5.8</v>
+        <v>5.7992</v>
       </c>
       <c r="J55" t="n">
         <v>-4701</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.33</v>
+        <v>-2.3303</v>
       </c>
       <c r="L55" t="n">
-        <v>50.81</v>
+        <v>50.8092</v>
       </c>
       <c r="M55" t="n">
-        <v>55.83</v>
+        <v>55.8338</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>168781</v>
       </c>
       <c r="R55" t="n">
-        <v>81.76000000000001</v>
+        <v>81.7595</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -4856,19 +4856,19 @@
         <v>25542</v>
       </c>
       <c r="I56" t="n">
-        <v>11.96</v>
+        <v>11.9626</v>
       </c>
       <c r="J56" t="n">
         <v>18087</v>
       </c>
       <c r="K56" t="n">
-        <v>8.470000000000001</v>
+        <v>8.471</v>
       </c>
       <c r="L56" t="n">
-        <v>51.62</v>
+        <v>51.6158</v>
       </c>
       <c r="M56" t="n">
-        <v>55.23</v>
+        <v>55.2267</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>162305</v>
       </c>
       <c r="R56" t="n">
-        <v>83.05</v>
+        <v>83.0506</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -4930,19 +4930,19 @@
         <v>27964</v>
       </c>
       <c r="I57" t="n">
-        <v>14.34</v>
+        <v>14.3441</v>
       </c>
       <c r="J57" t="n">
         <v>18727</v>
       </c>
       <c r="K57" t="n">
-        <v>9.609999999999999</v>
+        <v>9.606</v>
       </c>
       <c r="L57" t="n">
-        <v>51.55</v>
+        <v>51.554</v>
       </c>
       <c r="M57" t="n">
-        <v>53.23</v>
+        <v>53.2256</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>147192</v>
       </c>
       <c r="R57" t="n">
-        <v>83.53</v>
+        <v>83.52549999999999</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5004,19 +5004,19 @@
         <v>11569</v>
       </c>
       <c r="I58" t="n">
-        <v>6.79</v>
+        <v>6.7935</v>
       </c>
       <c r="J58" t="n">
         <v>5365</v>
       </c>
       <c r="K58" t="n">
-        <v>3.15</v>
+        <v>3.1504</v>
       </c>
       <c r="L58" t="n">
-        <v>51.1</v>
+        <v>51.096</v>
       </c>
       <c r="M58" t="n">
-        <v>56.62</v>
+        <v>56.6168</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>132246</v>
       </c>
       <c r="R58" t="n">
-        <v>80.18000000000001</v>
+        <v>80.1831</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5078,19 +5078,19 @@
         <v>19316</v>
       </c>
       <c r="I59" t="n">
-        <v>10.38</v>
+        <v>10.3791</v>
       </c>
       <c r="J59" t="n">
         <v>14089</v>
       </c>
       <c r="K59" t="n">
-        <v>7.57</v>
+        <v>7.5705</v>
       </c>
       <c r="L59" t="n">
-        <v>51.42</v>
+        <v>51.4218</v>
       </c>
       <c r="M59" t="n">
-        <v>54.56</v>
+        <v>54.5558</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>147788</v>
       </c>
       <c r="R59" t="n">
-        <v>85.92</v>
+        <v>85.9158</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5152,19 +5152,19 @@
         <v>18627</v>
       </c>
       <c r="I60" t="n">
-        <v>9.67</v>
+        <v>9.6732</v>
       </c>
       <c r="J60" t="n">
         <v>10872</v>
       </c>
       <c r="K60" t="n">
-        <v>5.65</v>
+        <v>5.646</v>
       </c>
       <c r="L60" t="n">
-        <v>50.77</v>
+        <v>50.766</v>
       </c>
       <c r="M60" t="n">
-        <v>55.89</v>
+        <v>55.8866</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>150497</v>
       </c>
       <c r="R60" t="n">
-        <v>82.83</v>
+        <v>82.8317</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5226,19 +5226,19 @@
         <v>10681</v>
       </c>
       <c r="I61" t="n">
-        <v>6.25</v>
+        <v>6.2544</v>
       </c>
       <c r="J61" t="n">
         <v>5119</v>
       </c>
       <c r="K61" t="n">
-        <v>3</v>
+        <v>2.9975</v>
       </c>
       <c r="L61" t="n">
-        <v>50.86</v>
+        <v>50.859</v>
       </c>
       <c r="M61" t="n">
-        <v>55.54</v>
+        <v>55.5379</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>134229</v>
       </c>
       <c r="R61" t="n">
-        <v>81.03</v>
+        <v>81.0283</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -5300,19 +5300,19 @@
         <v>16427</v>
       </c>
       <c r="I62" t="n">
-        <v>7.68</v>
+        <v>7.681</v>
       </c>
       <c r="J62" t="n">
         <v>9909</v>
       </c>
       <c r="K62" t="n">
-        <v>4.63</v>
+        <v>4.6333</v>
       </c>
       <c r="L62" t="n">
-        <v>52.21</v>
+        <v>52.211</v>
       </c>
       <c r="M62" t="n">
-        <v>59.09</v>
+        <v>59.0857</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>163151</v>
       </c>
       <c r="R62" t="n">
-        <v>79.98999999999999</v>
+        <v>79.9932</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -5374,19 +5374,19 @@
         <v>15372</v>
       </c>
       <c r="I63" t="n">
-        <v>7.65</v>
+        <v>7.653</v>
       </c>
       <c r="J63" t="n">
         <v>4023</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>2.0029</v>
       </c>
       <c r="L63" t="n">
-        <v>51.99</v>
+        <v>51.9854</v>
       </c>
       <c r="M63" t="n">
-        <v>58.05</v>
+        <v>58.0536</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>153735</v>
       </c>
       <c r="R63" t="n">
-        <v>78.09999999999999</v>
+        <v>78.1019</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -5448,19 +5448,19 @@
         <v>19689</v>
       </c>
       <c r="I64" t="n">
-        <v>8.960000000000001</v>
+        <v>8.9598</v>
       </c>
       <c r="J64" t="n">
         <v>1044</v>
       </c>
       <c r="K64" t="n">
-        <v>0.48</v>
+        <v>0.4751</v>
       </c>
       <c r="L64" t="n">
-        <v>52.26</v>
+        <v>52.2621</v>
       </c>
       <c r="M64" t="n">
-        <v>60</v>
+        <v>59.998</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>162039</v>
       </c>
       <c r="R64" t="n">
-        <v>74.09</v>
+        <v>74.09059999999999</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -5522,19 +5522,19 @@
         <v>20161</v>
       </c>
       <c r="I65" t="n">
-        <v>8.84</v>
+        <v>8.836600000000001</v>
       </c>
       <c r="J65" t="n">
         <v>5875</v>
       </c>
       <c r="K65" t="n">
-        <v>2.58</v>
+        <v>2.575</v>
       </c>
       <c r="L65" t="n">
-        <v>52.04</v>
+        <v>52.044</v>
       </c>
       <c r="M65" t="n">
-        <v>59.71</v>
+        <v>59.7143</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>171387</v>
       </c>
       <c r="R65" t="n">
-        <v>77.09999999999999</v>
+        <v>77.1048</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -5596,19 +5596,19 @@
         <v>23285</v>
       </c>
       <c r="I66" t="n">
-        <v>10.71</v>
+        <v>10.707</v>
       </c>
       <c r="J66" t="n">
         <v>15689</v>
       </c>
       <c r="K66" t="n">
-        <v>7.21</v>
+        <v>7.2142</v>
       </c>
       <c r="L66" t="n">
-        <v>52.42</v>
+        <v>52.4157</v>
       </c>
       <c r="M66" t="n">
-        <v>58.57</v>
+        <v>58.5699</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>163634</v>
       </c>
       <c r="R66" t="n">
-        <v>81.09</v>
+        <v>81.0928</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -5670,19 +5670,19 @@
         <v>32440</v>
       </c>
       <c r="I67" t="n">
-        <v>15.12</v>
+        <v>15.1183</v>
       </c>
       <c r="J67" t="n">
         <v>26180</v>
       </c>
       <c r="K67" t="n">
-        <v>12.2</v>
+        <v>12.2009</v>
       </c>
       <c r="L67" t="n">
-        <v>51.92</v>
+        <v>51.9222</v>
       </c>
       <c r="M67" t="n">
-        <v>55.03</v>
+        <v>55.0308</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>151990</v>
       </c>
       <c r="R67" t="n">
-        <v>80.68000000000001</v>
+        <v>80.67619999999999</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -5744,19 +5744,19 @@
         <v>34447</v>
       </c>
       <c r="I68" t="n">
-        <v>18.2</v>
+        <v>18.1991</v>
       </c>
       <c r="J68" t="n">
         <v>28054</v>
       </c>
       <c r="K68" t="n">
-        <v>14.82</v>
+        <v>14.8215</v>
       </c>
       <c r="L68" t="n">
-        <v>52.78</v>
+        <v>52.7792</v>
       </c>
       <c r="M68" t="n">
-        <v>54.47</v>
+        <v>54.475</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>124182</v>
       </c>
       <c r="R68" t="n">
-        <v>77.02</v>
+        <v>77.024</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -5818,19 +5818,19 @@
         <v>24398</v>
       </c>
       <c r="I69" t="n">
-        <v>11.14</v>
+        <v>11.1423</v>
       </c>
       <c r="J69" t="n">
         <v>15541</v>
       </c>
       <c r="K69" t="n">
-        <v>7.1</v>
+        <v>7.0974</v>
       </c>
       <c r="L69" t="n">
-        <v>52.65</v>
+        <v>52.647</v>
       </c>
       <c r="M69" t="n">
-        <v>57.62</v>
+        <v>57.6154</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>157535</v>
       </c>
       <c r="R69" t="n">
-        <v>77.44</v>
+        <v>77.4406</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -5892,19 +5892,19 @@
         <v>13230</v>
       </c>
       <c r="I70" t="n">
-        <v>7.46</v>
+        <v>7.4625</v>
       </c>
       <c r="J70" t="n">
         <v>-5429</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.06</v>
+        <v>-3.0623</v>
       </c>
       <c r="L70" t="n">
-        <v>53.29</v>
+        <v>53.2944</v>
       </c>
       <c r="M70" t="n">
-        <v>58.03</v>
+        <v>58.0272</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>142854</v>
       </c>
       <c r="R70" t="n">
-        <v>78.18000000000001</v>
+        <v>78.1836</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -5966,19 +5966,19 @@
         <v>19573</v>
       </c>
       <c r="I71" t="n">
-        <v>9.460000000000001</v>
+        <v>9.4621</v>
       </c>
       <c r="J71" t="n">
         <v>12264</v>
       </c>
       <c r="K71" t="n">
-        <v>5.93</v>
+        <v>5.9288</v>
       </c>
       <c r="L71" t="n">
-        <v>52.46</v>
+        <v>52.4621</v>
       </c>
       <c r="M71" t="n">
-        <v>59.78</v>
+        <v>59.7813</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>152241</v>
       </c>
       <c r="R71" t="n">
-        <v>78.23999999999999</v>
+        <v>78.236</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6040,19 +6040,19 @@
         <v>19937</v>
       </c>
       <c r="I72" t="n">
-        <v>9.76</v>
+        <v>9.758599999999999</v>
       </c>
       <c r="J72" t="n">
         <v>11925</v>
       </c>
       <c r="K72" t="n">
-        <v>5.84</v>
+        <v>5.8369</v>
       </c>
       <c r="L72" t="n">
-        <v>51.54</v>
+        <v>51.5374</v>
       </c>
       <c r="M72" t="n">
-        <v>58.25</v>
+        <v>58.2535</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>154161</v>
       </c>
       <c r="R72" t="n">
-        <v>80.13</v>
+        <v>80.1348</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -6114,19 +6114,19 @@
         <v>18368</v>
       </c>
       <c r="I73" t="n">
-        <v>9.58</v>
+        <v>9.581200000000001</v>
       </c>
       <c r="J73" t="n">
         <v>12501</v>
       </c>
       <c r="K73" t="n">
-        <v>6.52</v>
+        <v>6.5208</v>
       </c>
       <c r="L73" t="n">
-        <v>51.7</v>
+        <v>51.7008</v>
       </c>
       <c r="M73" t="n">
-        <v>57.58</v>
+        <v>57.5838</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>137931</v>
       </c>
       <c r="R73" t="n">
-        <v>76.97</v>
+        <v>76.967</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -6188,19 +6188,19 @@
         <v>14866</v>
       </c>
       <c r="I74" t="n">
-        <v>7.76</v>
+        <v>7.7611</v>
       </c>
       <c r="J74" t="n">
         <v>4334</v>
       </c>
       <c r="K74" t="n">
-        <v>2.26</v>
+        <v>2.2626</v>
       </c>
       <c r="L74" t="n">
-        <v>51.91</v>
+        <v>51.9134</v>
       </c>
       <c r="M74" t="n">
-        <v>57.14</v>
+        <v>57.1371</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>147912</v>
       </c>
       <c r="R74" t="n">
-        <v>79.01000000000001</v>
+        <v>79.0078</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -6262,19 +6262,19 @@
         <v>12737</v>
       </c>
       <c r="I75" t="n">
-        <v>7.06</v>
+        <v>7.0634</v>
       </c>
       <c r="J75" t="n">
         <v>26</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01</v>
+        <v>0.0144</v>
       </c>
       <c r="L75" t="n">
-        <v>50.84</v>
+        <v>50.8399</v>
       </c>
       <c r="M75" t="n">
-        <v>54.35</v>
+        <v>54.3456</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>147529</v>
       </c>
       <c r="R75" t="n">
-        <v>81.81999999999999</v>
+        <v>81.8246</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -6336,19 +6336,19 @@
         <v>17213</v>
       </c>
       <c r="I76" t="n">
-        <v>9.630000000000001</v>
+        <v>9.6288</v>
       </c>
       <c r="J76" t="n">
         <v>8362</v>
       </c>
       <c r="K76" t="n">
-        <v>4.68</v>
+        <v>4.6776</v>
       </c>
       <c r="L76" t="n">
-        <v>50.92</v>
+        <v>50.9208</v>
       </c>
       <c r="M76" t="n">
-        <v>54.6</v>
+        <v>54.5983</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>130848</v>
       </c>
       <c r="R76" t="n">
-        <v>76.79000000000001</v>
+        <v>76.7869</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -6410,19 +6410,19 @@
         <v>21392</v>
       </c>
       <c r="I77" t="n">
-        <v>10.72</v>
+        <v>10.7217</v>
       </c>
       <c r="J77" t="n">
         <v>5161</v>
       </c>
       <c r="K77" t="n">
-        <v>2.59</v>
+        <v>2.5867</v>
       </c>
       <c r="L77" t="n">
-        <v>51.41</v>
+        <v>51.4086</v>
       </c>
       <c r="M77" t="n">
-        <v>53.56</v>
+        <v>53.5574</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>158962</v>
       </c>
       <c r="R77" t="n">
-        <v>81.79000000000001</v>
+        <v>81.78740000000001</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -6484,19 +6484,19 @@
         <v>20707</v>
       </c>
       <c r="I78" t="n">
-        <v>10.22</v>
+        <v>10.2225</v>
       </c>
       <c r="J78" t="n">
         <v>4850</v>
       </c>
       <c r="K78" t="n">
-        <v>2.39</v>
+        <v>2.3943</v>
       </c>
       <c r="L78" t="n">
-        <v>51.51</v>
+        <v>51.5072</v>
       </c>
       <c r="M78" t="n">
-        <v>53.07</v>
+        <v>53.069</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>163345</v>
       </c>
       <c r="R78" t="n">
-        <v>82.62</v>
+        <v>82.6176</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -6558,19 +6558,19 @@
         <v>15692</v>
       </c>
       <c r="I79" t="n">
-        <v>7.91</v>
+        <v>7.9127</v>
       </c>
       <c r="J79" t="n">
         <v>6667</v>
       </c>
       <c r="K79" t="n">
-        <v>3.36</v>
+        <v>3.3619</v>
       </c>
       <c r="L79" t="n">
-        <v>51.62</v>
+        <v>51.6189</v>
       </c>
       <c r="M79" t="n">
-        <v>57.57</v>
+        <v>57.5707</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>159555</v>
       </c>
       <c r="R79" t="n">
-        <v>83.26000000000001</v>
+        <v>83.2551</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -6632,19 +6632,19 @@
         <v>16027</v>
       </c>
       <c r="I80" t="n">
-        <v>9.529999999999999</v>
+        <v>9.533200000000001</v>
       </c>
       <c r="J80" t="n">
         <v>6833</v>
       </c>
       <c r="K80" t="n">
-        <v>4.06</v>
+        <v>4.0644</v>
       </c>
       <c r="L80" t="n">
-        <v>51.54</v>
+        <v>51.5418</v>
       </c>
       <c r="M80" t="n">
-        <v>54.59</v>
+        <v>54.5891</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>131761</v>
       </c>
       <c r="R80" t="n">
-        <v>81.69</v>
+        <v>81.69450000000001</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -6706,19 +6706,19 @@
         <v>28231</v>
       </c>
       <c r="I81" t="n">
-        <v>15.77</v>
+        <v>15.7685</v>
       </c>
       <c r="J81" t="n">
         <v>13359</v>
       </c>
       <c r="K81" t="n">
-        <v>7.46</v>
+        <v>7.4617</v>
       </c>
       <c r="L81" t="n">
-        <v>51.56</v>
+        <v>51.5561</v>
       </c>
       <c r="M81" t="n">
-        <v>52.95</v>
+        <v>52.9453</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>134349</v>
       </c>
       <c r="R81" t="n">
-        <v>81.09</v>
+        <v>81.0919</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -6780,19 +6780,19 @@
         <v>36179</v>
       </c>
       <c r="I82" t="n">
-        <v>17.11</v>
+        <v>17.1123</v>
       </c>
       <c r="J82" t="n">
         <v>23498</v>
       </c>
       <c r="K82" t="n">
-        <v>11.11</v>
+        <v>11.1143</v>
       </c>
       <c r="L82" t="n">
-        <v>51.86</v>
+        <v>51.8633</v>
       </c>
       <c r="M82" t="n">
-        <v>52.96</v>
+        <v>52.9644</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>154527</v>
       </c>
       <c r="R82" t="n">
-        <v>82.23</v>
+        <v>82.2289</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -6854,19 +6854,19 @@
         <v>38879</v>
       </c>
       <c r="I83" t="n">
-        <v>23.55</v>
+        <v>23.5455</v>
       </c>
       <c r="J83" t="n">
         <v>28900</v>
       </c>
       <c r="K83" t="n">
-        <v>17.5</v>
+        <v>17.5021</v>
       </c>
       <c r="L83" t="n">
-        <v>51.37</v>
+        <v>51.3714</v>
       </c>
       <c r="M83" t="n">
-        <v>50.11</v>
+        <v>50.1067</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>107732</v>
       </c>
       <c r="R83" t="n">
-        <v>79.09</v>
+        <v>79.08499999999999</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -6928,19 +6928,19 @@
         <v>38341</v>
       </c>
       <c r="I84" t="n">
-        <v>19.16</v>
+        <v>19.1587</v>
       </c>
       <c r="J84" t="n">
         <v>23736</v>
       </c>
       <c r="K84" t="n">
-        <v>11.86</v>
+        <v>11.8607</v>
       </c>
       <c r="L84" t="n">
-        <v>51.9</v>
+        <v>51.9021</v>
       </c>
       <c r="M84" t="n">
-        <v>52.43</v>
+        <v>52.4321</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>140472</v>
       </c>
       <c r="R84" t="n">
-        <v>79.64</v>
+        <v>79.63849999999999</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -7002,19 +7002,19 @@
         <v>13047</v>
       </c>
       <c r="I85" t="n">
-        <v>6.91</v>
+        <v>6.9111</v>
       </c>
       <c r="J85" t="n">
         <v>493</v>
       </c>
       <c r="K85" t="n">
-        <v>0.26</v>
+        <v>0.2611</v>
       </c>
       <c r="L85" t="n">
-        <v>51.15</v>
+        <v>51.1484</v>
       </c>
       <c r="M85" t="n">
-        <v>53.68</v>
+        <v>53.6752</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>161066</v>
       </c>
       <c r="R85" t="n">
-        <v>85.54000000000001</v>
+        <v>85.541</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -7076,19 +7076,19 @@
         <v>21303</v>
       </c>
       <c r="I86" t="n">
-        <v>10.32</v>
+        <v>10.3167</v>
       </c>
       <c r="J86" t="n">
         <v>11069</v>
       </c>
       <c r="K86" t="n">
-        <v>5.36</v>
+        <v>5.3606</v>
       </c>
       <c r="L86" t="n">
-        <v>51.82</v>
+        <v>51.8243</v>
       </c>
       <c r="M86" t="n">
-        <v>54.34</v>
+        <v>54.3398</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>152386</v>
       </c>
       <c r="R86" t="n">
-        <v>77.98</v>
+        <v>77.9783</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -7150,19 +7150,19 @@
         <v>15270</v>
       </c>
       <c r="I87" t="n">
-        <v>8.130000000000001</v>
+        <v>8.131399999999999</v>
       </c>
       <c r="J87" t="n">
         <v>1537</v>
       </c>
       <c r="K87" t="n">
-        <v>0.82</v>
+        <v>0.8185</v>
       </c>
       <c r="L87" t="n">
-        <v>50.64</v>
+        <v>50.6382</v>
       </c>
       <c r="M87" t="n">
-        <v>51.67</v>
+        <v>51.6699</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>148131</v>
       </c>
       <c r="R87" t="n">
-        <v>79.53</v>
+        <v>79.5317</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -7224,19 +7224,19 @@
         <v>12445</v>
       </c>
       <c r="I88" t="n">
-        <v>7.25</v>
+        <v>7.2466</v>
       </c>
       <c r="J88" t="n">
         <v>-233</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.14</v>
+        <v>-0.1357</v>
       </c>
       <c r="L88" t="n">
-        <v>50.73</v>
+        <v>50.734</v>
       </c>
       <c r="M88" t="n">
-        <v>54.54</v>
+        <v>54.544</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>139091</v>
       </c>
       <c r="R88" t="n">
-        <v>80.88</v>
+        <v>80.8819</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -7298,19 +7298,19 @@
         <v>30228</v>
       </c>
       <c r="I89" t="n">
-        <v>18.06</v>
+        <v>18.0638</v>
       </c>
       <c r="J89" t="n">
         <v>25075</v>
       </c>
       <c r="K89" t="n">
-        <v>14.98</v>
+        <v>14.9845</v>
       </c>
       <c r="L89" t="n">
-        <v>51</v>
+        <v>50.9998</v>
       </c>
       <c r="M89" t="n">
-        <v>52.58</v>
+        <v>52.5771</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>112135</v>
       </c>
       <c r="R89" t="n">
-        <v>78.81999999999999</v>
+        <v>78.8212</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -7372,19 +7372,19 @@
         <v>23254</v>
       </c>
       <c r="I90" t="n">
-        <v>13.64</v>
+        <v>13.6422</v>
       </c>
       <c r="J90" t="n">
         <v>20153</v>
       </c>
       <c r="K90" t="n">
-        <v>11.82</v>
+        <v>11.823</v>
       </c>
       <c r="L90" t="n">
-        <v>50.79</v>
+        <v>50.7932</v>
       </c>
       <c r="M90" t="n">
-        <v>52.77</v>
+        <v>52.7651</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>121356</v>
       </c>
       <c r="R90" t="n">
-        <v>80.73999999999999</v>
+        <v>80.7409</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -7446,19 +7446,19 @@
         <v>15431</v>
       </c>
       <c r="I91" t="n">
-        <v>8.050000000000001</v>
+        <v>8.052199999999999</v>
       </c>
       <c r="J91" t="n">
         <v>3141</v>
       </c>
       <c r="K91" t="n">
-        <v>1.64</v>
+        <v>1.639</v>
       </c>
       <c r="L91" t="n">
-        <v>50.62</v>
+        <v>50.6199</v>
       </c>
       <c r="M91" t="n">
-        <v>53.78</v>
+        <v>53.7813</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>146166</v>
       </c>
       <c r="R91" t="n">
-        <v>77.54000000000001</v>
+        <v>77.5437</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -7520,19 +7520,19 @@
         <v>24075</v>
       </c>
       <c r="I92" t="n">
-        <v>12.85</v>
+        <v>12.8495</v>
       </c>
       <c r="J92" t="n">
         <v>19539</v>
       </c>
       <c r="K92" t="n">
-        <v>10.43</v>
+        <v>10.4285</v>
       </c>
       <c r="L92" t="n">
-        <v>50.94</v>
+        <v>50.9423</v>
       </c>
       <c r="M92" t="n">
-        <v>54.66</v>
+        <v>54.6625</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>128447</v>
       </c>
       <c r="R92" t="n">
-        <v>76.54000000000001</v>
+        <v>76.5376</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -7594,19 +7594,19 @@
         <v>24743</v>
       </c>
       <c r="I93" t="n">
-        <v>13.95</v>
+        <v>13.9539</v>
       </c>
       <c r="J93" t="n">
         <v>20777</v>
       </c>
       <c r="K93" t="n">
-        <v>11.72</v>
+        <v>11.7173</v>
       </c>
       <c r="L93" t="n">
-        <v>51.17</v>
+        <v>51.1694</v>
       </c>
       <c r="M93" t="n">
-        <v>54.3</v>
+        <v>54.2982</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>122652</v>
       </c>
       <c r="R93" t="n">
-        <v>78.34999999999999</v>
+        <v>78.3509</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -7668,19 +7668,19 @@
         <v>16193</v>
       </c>
       <c r="I94" t="n">
-        <v>8.69</v>
+        <v>8.695</v>
       </c>
       <c r="J94" t="n">
         <v>9649</v>
       </c>
       <c r="K94" t="n">
-        <v>5.18</v>
+        <v>5.1811</v>
       </c>
       <c r="L94" t="n">
-        <v>51.63</v>
+        <v>51.6313</v>
       </c>
       <c r="M94" t="n">
-        <v>56.04</v>
+        <v>56.0366</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135851</v>
       </c>
       <c r="R94" t="n">
-        <v>76.93000000000001</v>
+        <v>76.9324</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -7742,19 +7742,19 @@
         <v>16683</v>
       </c>
       <c r="I95" t="n">
-        <v>8.880000000000001</v>
+        <v>8.883900000000001</v>
       </c>
       <c r="J95" t="n">
         <v>11885</v>
       </c>
       <c r="K95" t="n">
-        <v>6.33</v>
+        <v>6.3289</v>
       </c>
       <c r="L95" t="n">
-        <v>51.43</v>
+        <v>51.4346</v>
       </c>
       <c r="M95" t="n">
-        <v>54.64</v>
+        <v>54.6425</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>124752</v>
       </c>
       <c r="R95" t="n">
-        <v>70.92</v>
+        <v>70.92010000000001</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -7816,19 +7816,19 @@
         <v>13948</v>
       </c>
       <c r="I96" t="n">
-        <v>8.51</v>
+        <v>8.5059</v>
       </c>
       <c r="J96" t="n">
         <v>8024</v>
       </c>
       <c r="K96" t="n">
-        <v>4.89</v>
+        <v>4.8932</v>
       </c>
       <c r="L96" t="n">
-        <v>51.57</v>
+        <v>51.5743</v>
       </c>
       <c r="M96" t="n">
-        <v>55.81</v>
+        <v>55.8073</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>126238</v>
       </c>
       <c r="R96" t="n">
-        <v>80.94</v>
+        <v>80.94410000000001</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -7890,19 +7890,19 @@
         <v>17424</v>
       </c>
       <c r="I97" t="n">
-        <v>10.32</v>
+        <v>10.3193</v>
       </c>
       <c r="J97" t="n">
         <v>10592</v>
       </c>
       <c r="K97" t="n">
-        <v>6.27</v>
+        <v>6.2731</v>
       </c>
       <c r="L97" t="n">
-        <v>51.38</v>
+        <v>51.3817</v>
       </c>
       <c r="M97" t="n">
-        <v>54.53</v>
+        <v>54.534</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>122912</v>
       </c>
       <c r="R97" t="n">
-        <v>77.67</v>
+        <v>77.6666</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -7964,19 +7964,19 @@
         <v>20979</v>
       </c>
       <c r="I98" t="n">
-        <v>12.77</v>
+        <v>12.7679</v>
       </c>
       <c r="J98" t="n">
         <v>14738</v>
       </c>
       <c r="K98" t="n">
-        <v>8.970000000000001</v>
+        <v>8.9696</v>
       </c>
       <c r="L98" t="n">
-        <v>51.98</v>
+        <v>51.9801</v>
       </c>
       <c r="M98" t="n">
-        <v>53.03</v>
+        <v>53.0292</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>113747</v>
       </c>
       <c r="R98" t="n">
-        <v>76.05</v>
+        <v>76.0478</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -8038,19 +8038,19 @@
         <v>14972</v>
       </c>
       <c r="I99" t="n">
-        <v>8.289999999999999</v>
+        <v>8.2905</v>
       </c>
       <c r="J99" t="n">
         <v>10339</v>
       </c>
       <c r="K99" t="n">
-        <v>5.73</v>
+        <v>5.725</v>
       </c>
       <c r="L99" t="n">
-        <v>51.43</v>
+        <v>51.4267</v>
       </c>
       <c r="M99" t="n">
-        <v>53.51</v>
+        <v>53.5065</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>128180</v>
       </c>
       <c r="R99" t="n">
-        <v>75.29000000000001</v>
+        <v>75.28749999999999</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -8112,19 +8112,19 @@
         <v>18966</v>
       </c>
       <c r="I100" t="n">
-        <v>10.93</v>
+        <v>10.9274</v>
       </c>
       <c r="J100" t="n">
         <v>10678</v>
       </c>
       <c r="K100" t="n">
-        <v>6.15</v>
+        <v>6.1522</v>
       </c>
       <c r="L100" t="n">
-        <v>52.19</v>
+        <v>52.1937</v>
       </c>
       <c r="M100" t="n">
-        <v>55.15</v>
+        <v>55.1513</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>121150</v>
       </c>
       <c r="R100" t="n">
-        <v>74.38</v>
+        <v>74.3776</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -8186,19 +8186,19 @@
         <v>18678</v>
       </c>
       <c r="I101" t="n">
-        <v>9.9</v>
+        <v>9.902100000000001</v>
       </c>
       <c r="J101" t="n">
         <v>11126</v>
       </c>
       <c r="K101" t="n">
-        <v>5.9</v>
+        <v>5.8984</v>
       </c>
       <c r="L101" t="n">
-        <v>51.59</v>
+        <v>51.592</v>
       </c>
       <c r="M101" t="n">
-        <v>53.74</v>
+        <v>53.7424</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>135988</v>
       </c>
       <c r="R101" t="n">
-        <v>76.61</v>
+        <v>76.613</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -8260,19 +8260,19 @@
         <v>17945</v>
       </c>
       <c r="I102" t="n">
-        <v>9.369999999999999</v>
+        <v>9.3667</v>
       </c>
       <c r="J102" t="n">
         <v>6917</v>
       </c>
       <c r="K102" t="n">
-        <v>3.61</v>
+        <v>3.6105</v>
       </c>
       <c r="L102" t="n">
-        <v>50.5</v>
+        <v>50.4964</v>
       </c>
       <c r="M102" t="n">
-        <v>52.97</v>
+        <v>52.973</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>144794</v>
       </c>
       <c r="R102" t="n">
-        <v>78.41</v>
+        <v>78.40900000000001</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -8334,19 +8334,19 @@
         <v>13759</v>
       </c>
       <c r="I103" t="n">
-        <v>6.96</v>
+        <v>6.9623</v>
       </c>
       <c r="J103" t="n">
         <v>6156</v>
       </c>
       <c r="K103" t="n">
-        <v>3.12</v>
+        <v>3.1151</v>
       </c>
       <c r="L103" t="n">
-        <v>51.27</v>
+        <v>51.2739</v>
       </c>
       <c r="M103" t="n">
-        <v>56.89</v>
+        <v>56.8864</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>161974</v>
       </c>
       <c r="R103" t="n">
-        <v>84.59999999999999</v>
+        <v>84.5972</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -8408,19 +8408,19 @@
         <v>11802</v>
       </c>
       <c r="I104" t="n">
-        <v>5.59</v>
+        <v>5.5943</v>
       </c>
       <c r="J104" t="n">
         <v>4947</v>
       </c>
       <c r="K104" t="n">
-        <v>2.34</v>
+        <v>2.345</v>
       </c>
       <c r="L104" t="n">
-        <v>51.66</v>
+        <v>51.6593</v>
       </c>
       <c r="M104" t="n">
-        <v>56.12</v>
+        <v>56.1176</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>172221</v>
       </c>
       <c r="R104" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5959</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -8482,19 +8482,19 @@
         <v>16291</v>
       </c>
       <c r="I105" t="n">
-        <v>8.24</v>
+        <v>8.241199999999999</v>
       </c>
       <c r="J105" t="n">
         <v>5797</v>
       </c>
       <c r="K105" t="n">
-        <v>2.93</v>
+        <v>2.9326</v>
       </c>
       <c r="L105" t="n">
-        <v>51.57</v>
+        <v>51.5675</v>
       </c>
       <c r="M105" t="n">
-        <v>55.82</v>
+        <v>55.8161</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>157661</v>
       </c>
       <c r="R105" t="n">
-        <v>82.17</v>
+        <v>82.1665</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -8556,19 +8556,19 @@
         <v>16689</v>
       </c>
       <c r="I106" t="n">
-        <v>9.52</v>
+        <v>9.5158</v>
       </c>
       <c r="J106" t="n">
         <v>4179</v>
       </c>
       <c r="K106" t="n">
-        <v>2.38</v>
+        <v>2.3828</v>
       </c>
       <c r="L106" t="n">
-        <v>51.63</v>
+        <v>51.6262</v>
       </c>
       <c r="M106" t="n">
-        <v>55.25</v>
+        <v>55.252</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>140781</v>
       </c>
       <c r="R106" t="n">
-        <v>82.23</v>
+        <v>82.23050000000001</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -8630,19 +8630,19 @@
         <v>13080</v>
       </c>
       <c r="I107" t="n">
-        <v>8.01</v>
+        <v>8.0113</v>
       </c>
       <c r="J107" t="n">
         <v>9288</v>
       </c>
       <c r="K107" t="n">
-        <v>5.69</v>
+        <v>5.6888</v>
       </c>
       <c r="L107" t="n">
-        <v>51.21</v>
+        <v>51.213</v>
       </c>
       <c r="M107" t="n">
-        <v>55.02</v>
+        <v>55.0153</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>112560</v>
       </c>
       <c r="R107" t="n">
-        <v>73.09999999999999</v>
+        <v>73.09990000000001</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -8704,19 +8704,19 @@
         <v>14189</v>
       </c>
       <c r="I108" t="n">
-        <v>7.36</v>
+        <v>7.3636</v>
       </c>
       <c r="J108" t="n">
         <v>8234</v>
       </c>
       <c r="K108" t="n">
-        <v>4.27</v>
+        <v>4.2732</v>
       </c>
       <c r="L108" t="n">
-        <v>52.8</v>
+        <v>52.8022</v>
       </c>
       <c r="M108" t="n">
-        <v>56.73</v>
+        <v>56.727</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>144837</v>
       </c>
       <c r="R108" t="n">
-        <v>78.52</v>
+        <v>78.52070000000001</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -8778,19 +8778,19 @@
         <v>17320</v>
       </c>
       <c r="I109" t="n">
-        <v>8.18</v>
+        <v>8.1838</v>
       </c>
       <c r="J109" t="n">
         <v>10244</v>
       </c>
       <c r="K109" t="n">
-        <v>4.84</v>
+        <v>4.8403</v>
       </c>
       <c r="L109" t="n">
-        <v>52.64</v>
+        <v>52.6441</v>
       </c>
       <c r="M109" t="n">
-        <v>55.83</v>
+        <v>55.8256</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>155399</v>
       </c>
       <c r="R109" t="n">
-        <v>77.16</v>
+        <v>77.1617</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -8852,19 +8852,19 @@
         <v>17301</v>
       </c>
       <c r="I110" t="n">
-        <v>8.49</v>
+        <v>8.4862</v>
       </c>
       <c r="J110" t="n">
         <v>11438</v>
       </c>
       <c r="K110" t="n">
-        <v>5.61</v>
+        <v>5.6104</v>
       </c>
       <c r="L110" t="n">
-        <v>53.57</v>
+        <v>53.5677</v>
       </c>
       <c r="M110" t="n">
-        <v>58.5</v>
+        <v>58.4995</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>142667</v>
       </c>
       <c r="R110" t="n">
-        <v>74.14</v>
+        <v>74.1378</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -8926,19 +8926,19 @@
         <v>17172</v>
       </c>
       <c r="I111" t="n">
-        <v>8.539999999999999</v>
+        <v>8.5412</v>
       </c>
       <c r="J111" t="n">
         <v>11184</v>
       </c>
       <c r="K111" t="n">
-        <v>5.56</v>
+        <v>5.5628</v>
       </c>
       <c r="L111" t="n">
-        <v>53.08</v>
+        <v>53.0763</v>
       </c>
       <c r="M111" t="n">
-        <v>59.1</v>
+        <v>59.0962</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>137435</v>
       </c>
       <c r="R111" t="n">
-        <v>72.39</v>
+        <v>72.3853</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -9000,19 +9000,19 @@
         <v>22628</v>
       </c>
       <c r="I112" t="n">
-        <v>10.58</v>
+        <v>10.5844</v>
       </c>
       <c r="J112" t="n">
         <v>15391</v>
       </c>
       <c r="K112" t="n">
-        <v>7.2</v>
+        <v>7.1993</v>
       </c>
       <c r="L112" t="n">
-        <v>52.55</v>
+        <v>52.5526</v>
       </c>
       <c r="M112" t="n">
-        <v>56.9</v>
+        <v>56.903</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>140745</v>
       </c>
       <c r="R112" t="n">
-        <v>70.94</v>
+        <v>70.9418</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -9074,19 +9074,19 @@
         <v>19744</v>
       </c>
       <c r="I113" t="n">
-        <v>10.31</v>
+        <v>10.3085</v>
       </c>
       <c r="J113" t="n">
         <v>15517</v>
       </c>
       <c r="K113" t="n">
-        <v>8.1</v>
+        <v>8.1015</v>
       </c>
       <c r="L113" t="n">
-        <v>51.92</v>
+        <v>51.9198</v>
       </c>
       <c r="M113" t="n">
-        <v>56.67</v>
+        <v>56.6704</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>123843</v>
       </c>
       <c r="R113" t="n">
-        <v>70.36</v>
+        <v>70.3593</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -9148,19 +9148,19 @@
         <v>28964</v>
       </c>
       <c r="I114" t="n">
-        <v>12.22</v>
+        <v>12.2181</v>
       </c>
       <c r="J114" t="n">
         <v>21890</v>
       </c>
       <c r="K114" t="n">
-        <v>9.23</v>
+        <v>9.234</v>
       </c>
       <c r="L114" t="n">
-        <v>52.64</v>
+        <v>52.6382</v>
       </c>
       <c r="M114" t="n">
-        <v>56.32</v>
+        <v>56.3216</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>157450</v>
       </c>
       <c r="R114" t="n">
-        <v>73.18000000000001</v>
+        <v>73.1754</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -9222,19 +9222,19 @@
         <v>16015</v>
       </c>
       <c r="I115" t="n">
-        <v>8</v>
+        <v>8.0037</v>
       </c>
       <c r="J115" t="n">
         <v>10730</v>
       </c>
       <c r="K115" t="n">
-        <v>5.36</v>
+        <v>5.3624</v>
       </c>
       <c r="L115" t="n">
-        <v>52.92</v>
+        <v>52.9246</v>
       </c>
       <c r="M115" t="n">
-        <v>57.41</v>
+        <v>57.4087</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>135405</v>
       </c>
       <c r="R115" t="n">
-        <v>71.5</v>
+        <v>71.5044</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -9296,19 +9296,19 @@
         <v>15485</v>
       </c>
       <c r="I116" t="n">
-        <v>7.37</v>
+        <v>7.3739</v>
       </c>
       <c r="J116" t="n">
         <v>8796</v>
       </c>
       <c r="K116" t="n">
-        <v>4.19</v>
+        <v>4.1887</v>
       </c>
       <c r="L116" t="n">
-        <v>53.19</v>
+        <v>53.1891</v>
       </c>
       <c r="M116" t="n">
-        <v>56.73</v>
+        <v>56.7323</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>149670</v>
       </c>
       <c r="R116" t="n">
-        <v>74.39</v>
+        <v>74.3887</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -9370,19 +9370,19 @@
         <v>12076</v>
       </c>
       <c r="I117" t="n">
-        <v>5.61</v>
+        <v>5.6122</v>
       </c>
       <c r="J117" t="n">
         <v>663</v>
       </c>
       <c r="K117" t="n">
-        <v>0.31</v>
+        <v>0.3081</v>
       </c>
       <c r="L117" t="n">
-        <v>51.52</v>
+        <v>51.522</v>
       </c>
       <c r="M117" t="n">
-        <v>55.47</v>
+        <v>55.4737</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>172736</v>
       </c>
       <c r="R117" t="n">
-        <v>80.52</v>
+        <v>80.5247</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -9444,19 +9444,19 @@
         <v>13126</v>
       </c>
       <c r="I118" t="n">
-        <v>7.25</v>
+        <v>7.2494</v>
       </c>
       <c r="J118" t="n">
         <v>2266</v>
       </c>
       <c r="K118" t="n">
-        <v>1.25</v>
+        <v>1.2515</v>
       </c>
       <c r="L118" t="n">
-        <v>51.46</v>
+        <v>51.4625</v>
       </c>
       <c r="M118" t="n">
-        <v>53.17</v>
+        <v>53.1693</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>142344</v>
       </c>
       <c r="R118" t="n">
-        <v>79.61</v>
+        <v>79.6116</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -9518,19 +9518,19 @@
         <v>10057</v>
       </c>
       <c r="I119" t="n">
-        <v>4.88</v>
+        <v>4.882</v>
       </c>
       <c r="J119" t="n">
         <v>307</v>
       </c>
       <c r="K119" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="L119" t="n">
-        <v>52.6</v>
+        <v>52.6046</v>
       </c>
       <c r="M119" t="n">
-        <v>56.15</v>
+        <v>56.1499</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>164101</v>
       </c>
       <c r="R119" t="n">
-        <v>79.78</v>
+        <v>79.7792</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -9592,19 +9592,19 @@
         <v>14141</v>
       </c>
       <c r="I120" t="n">
-        <v>7.03</v>
+        <v>7.0291</v>
       </c>
       <c r="J120" t="n">
         <v>7905</v>
       </c>
       <c r="K120" t="n">
-        <v>3.93</v>
+        <v>3.9294</v>
       </c>
       <c r="L120" t="n">
-        <v>52.89</v>
+        <v>52.8853</v>
       </c>
       <c r="M120" t="n">
-        <v>56.98</v>
+        <v>56.9832</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>148854</v>
       </c>
       <c r="R120" t="n">
-        <v>77.02</v>
+        <v>77.0179</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -9666,19 +9666,19 @@
         <v>14408</v>
       </c>
       <c r="I121" t="n">
-        <v>7.76</v>
+        <v>7.764</v>
       </c>
       <c r="J121" t="n">
         <v>5791</v>
       </c>
       <c r="K121" t="n">
-        <v>3.12</v>
+        <v>3.1206</v>
       </c>
       <c r="L121" t="n">
-        <v>52.97</v>
+        <v>52.9692</v>
       </c>
       <c r="M121" t="n">
-        <v>55.34</v>
+        <v>55.3373</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>137623</v>
       </c>
       <c r="R121" t="n">
-        <v>76.55</v>
+        <v>76.54949999999999</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -9740,19 +9740,19 @@
         <v>16208</v>
       </c>
       <c r="I122" t="n">
-        <v>7.85</v>
+        <v>7.8484</v>
       </c>
       <c r="J122" t="n">
         <v>9168</v>
       </c>
       <c r="K122" t="n">
-        <v>4.44</v>
+        <v>4.4394</v>
       </c>
       <c r="L122" t="n">
-        <v>52.61</v>
+        <v>52.6139</v>
       </c>
       <c r="M122" t="n">
-        <v>54.17</v>
+        <v>54.1708</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>142556</v>
       </c>
       <c r="R122" t="n">
-        <v>72.23999999999999</v>
+        <v>72.2366</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -9814,19 +9814,19 @@
         <v>12096</v>
       </c>
       <c r="I123" t="n">
-        <v>5.94</v>
+        <v>5.9443</v>
       </c>
       <c r="J123" t="n">
         <v>1773</v>
       </c>
       <c r="K123" t="n">
-        <v>0.87</v>
+        <v>0.8713</v>
       </c>
       <c r="L123" t="n">
-        <v>52.92</v>
+        <v>52.9213</v>
       </c>
       <c r="M123" t="n">
-        <v>55.58</v>
+        <v>55.5804</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>153260</v>
       </c>
       <c r="R123" t="n">
-        <v>75.98</v>
+        <v>75.9781</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -9888,19 +9888,19 @@
         <v>14189</v>
       </c>
       <c r="I124" t="n">
-        <v>6.82</v>
+        <v>6.8163</v>
       </c>
       <c r="J124" t="n">
         <v>1698</v>
       </c>
       <c r="K124" t="n">
-        <v>0.82</v>
+        <v>0.8157</v>
       </c>
       <c r="L124" t="n">
-        <v>52.41</v>
+        <v>52.4125</v>
       </c>
       <c r="M124" t="n">
-        <v>54.08</v>
+        <v>54.0841</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>164414</v>
       </c>
       <c r="R124" t="n">
-        <v>79.63</v>
+        <v>79.63330000000001</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -9962,19 +9962,19 @@
         <v>16620</v>
       </c>
       <c r="I125" t="n">
-        <v>9.59</v>
+        <v>9.5916</v>
       </c>
       <c r="J125" t="n">
         <v>8736</v>
       </c>
       <c r="K125" t="n">
-        <v>5.04</v>
+        <v>5.0416</v>
       </c>
       <c r="L125" t="n">
-        <v>52</v>
+        <v>52.0029</v>
       </c>
       <c r="M125" t="n">
-        <v>53.27</v>
+        <v>53.2732</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>129690</v>
       </c>
       <c r="R125" t="n">
-        <v>78.81999999999999</v>
+        <v>78.8193</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -10036,19 +10036,19 @@
         <v>17458</v>
       </c>
       <c r="I126" t="n">
-        <v>9.98</v>
+        <v>9.979900000000001</v>
       </c>
       <c r="J126" t="n">
         <v>6066</v>
       </c>
       <c r="K126" t="n">
-        <v>3.47</v>
+        <v>3.4677</v>
       </c>
       <c r="L126" t="n">
-        <v>52</v>
+        <v>52.0039</v>
       </c>
       <c r="M126" t="n">
-        <v>52.29</v>
+        <v>52.2855</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>132384</v>
       </c>
       <c r="R126" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3964</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>16112</v>
       </c>
       <c r="I127" t="n">
-        <v>8.710000000000001</v>
+        <v>8.7087</v>
       </c>
       <c r="J127" t="n">
         <v>8011</v>
@@ -10119,10 +10119,10 @@
         <v>4.33</v>
       </c>
       <c r="L127" t="n">
-        <v>53.37</v>
+        <v>53.3676</v>
       </c>
       <c r="M127" t="n">
-        <v>53.28</v>
+        <v>53.2771</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>136507</v>
       </c>
       <c r="R127" t="n">
-        <v>77.12</v>
+        <v>77.12260000000001</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -10184,19 +10184,19 @@
         <v>12394</v>
       </c>
       <c r="I128" t="n">
-        <v>6.55</v>
+        <v>6.5487</v>
       </c>
       <c r="J128" t="n">
         <v>5979</v>
       </c>
       <c r="K128" t="n">
-        <v>3.16</v>
+        <v>3.1592</v>
       </c>
       <c r="L128" t="n">
-        <v>53.36</v>
+        <v>53.3597</v>
       </c>
       <c r="M128" t="n">
-        <v>53.45</v>
+        <v>53.4533</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>138231</v>
       </c>
       <c r="R128" t="n">
-        <v>75.42</v>
+        <v>75.4207</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -10258,19 +10258,19 @@
         <v>14901</v>
       </c>
       <c r="I129" t="n">
-        <v>7.25</v>
+        <v>7.2489</v>
       </c>
       <c r="J129" t="n">
         <v>7617</v>
       </c>
       <c r="K129" t="n">
-        <v>3.71</v>
+        <v>3.7055</v>
       </c>
       <c r="L129" t="n">
-        <v>53.96</v>
+        <v>53.9604</v>
       </c>
       <c r="M129" t="n">
-        <v>53.59</v>
+        <v>53.5937</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>149916</v>
       </c>
       <c r="R129" t="n">
-        <v>75.73999999999999</v>
+        <v>75.7362</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -10332,19 +10332,19 @@
         <v>16330</v>
       </c>
       <c r="I130" t="n">
-        <v>8.029999999999999</v>
+        <v>8.030799999999999</v>
       </c>
       <c r="J130" t="n">
         <v>8046</v>
       </c>
       <c r="K130" t="n">
-        <v>3.96</v>
+        <v>3.9569</v>
       </c>
       <c r="L130" t="n">
-        <v>54.03</v>
+        <v>54.0331</v>
       </c>
       <c r="M130" t="n">
-        <v>54.51</v>
+        <v>54.507</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>147566</v>
       </c>
       <c r="R130" t="n">
-        <v>75.56</v>
+        <v>75.56019999999999</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -10406,19 +10406,19 @@
         <v>23095</v>
       </c>
       <c r="I131" t="n">
-        <v>10.9</v>
+        <v>10.9006</v>
       </c>
       <c r="J131" t="n">
         <v>13827</v>
       </c>
       <c r="K131" t="n">
-        <v>6.53</v>
+        <v>6.5262</v>
       </c>
       <c r="L131" t="n">
-        <v>52.65</v>
+        <v>52.6528</v>
       </c>
       <c r="M131" t="n">
-        <v>53.8</v>
+        <v>53.7952</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>158894</v>
       </c>
       <c r="R131" t="n">
-        <v>80.23</v>
+        <v>80.2325</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -10480,19 +10480,19 @@
         <v>20852</v>
       </c>
       <c r="I132" t="n">
-        <v>10.34</v>
+        <v>10.3352</v>
       </c>
       <c r="J132" t="n">
         <v>13929</v>
       </c>
       <c r="K132" t="n">
-        <v>6.9</v>
+        <v>6.9038</v>
       </c>
       <c r="L132" t="n">
-        <v>53.26</v>
+        <v>53.2646</v>
       </c>
       <c r="M132" t="n">
-        <v>54.86</v>
+        <v>54.858</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>149082</v>
       </c>
       <c r="R132" t="n">
-        <v>79.37</v>
+        <v>79.3716</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -10554,19 +10554,19 @@
         <v>39117</v>
       </c>
       <c r="I133" t="n">
-        <v>20.05</v>
+        <v>20.0507</v>
       </c>
       <c r="J133" t="n">
         <v>30529</v>
       </c>
       <c r="K133" t="n">
-        <v>15.65</v>
+        <v>15.6487</v>
       </c>
       <c r="L133" t="n">
-        <v>52.17</v>
+        <v>52.1734</v>
       </c>
       <c r="M133" t="n">
-        <v>51.92</v>
+        <v>51.9237</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>131587</v>
       </c>
       <c r="R133" t="n">
-        <v>79.95999999999999</v>
+        <v>79.9624</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -10628,19 +10628,19 @@
         <v>48675</v>
       </c>
       <c r="I134" t="n">
-        <v>23.79</v>
+        <v>23.7929</v>
       </c>
       <c r="J134" t="n">
         <v>39306</v>
       </c>
       <c r="K134" t="n">
-        <v>19.21</v>
+        <v>19.2132</v>
       </c>
       <c r="L134" t="n">
-        <v>52.42</v>
+        <v>52.4211</v>
       </c>
       <c r="M134" t="n">
-        <v>52.25</v>
+        <v>52.2465</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>129765</v>
       </c>
       <c r="R134" t="n">
-        <v>78.52</v>
+        <v>78.51600000000001</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -10702,19 +10702,19 @@
         <v>53154</v>
       </c>
       <c r="I135" t="n">
-        <v>26.1</v>
+        <v>26.1036</v>
       </c>
       <c r="J135" t="n">
         <v>45082</v>
       </c>
       <c r="K135" t="n">
-        <v>22.14</v>
+        <v>22.1395</v>
       </c>
       <c r="L135" t="n">
-        <v>51.68</v>
+        <v>51.6778</v>
       </c>
       <c r="M135" t="n">
-        <v>50.96</v>
+        <v>50.9557</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>120488</v>
       </c>
       <c r="R135" t="n">
-        <v>76</v>
+        <v>75.9961</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -10776,19 +10776,19 @@
         <v>44551</v>
       </c>
       <c r="I136" t="n">
-        <v>21.59</v>
+        <v>21.5882</v>
       </c>
       <c r="J136" t="n">
         <v>35189</v>
       </c>
       <c r="K136" t="n">
-        <v>17.05</v>
+        <v>17.0517</v>
       </c>
       <c r="L136" t="n">
-        <v>51.77</v>
+        <v>51.7738</v>
       </c>
       <c r="M136" t="n">
-        <v>51.96</v>
+        <v>51.9607</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>140355</v>
       </c>
       <c r="R136" t="n">
-        <v>81.98999999999999</v>
+        <v>81.9936</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -10850,19 +10850,19 @@
         <v>20765</v>
       </c>
       <c r="I137" t="n">
-        <v>10.63</v>
+        <v>10.6342</v>
       </c>
       <c r="J137" t="n">
         <v>13958</v>
       </c>
       <c r="K137" t="n">
-        <v>7.15</v>
+        <v>7.1482</v>
       </c>
       <c r="L137" t="n">
-        <v>52.83</v>
+        <v>52.8295</v>
       </c>
       <c r="M137" t="n">
-        <v>55.73</v>
+        <v>55.7332</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>146878</v>
       </c>
       <c r="R137" t="n">
-        <v>81.01000000000001</v>
+        <v>81.0102</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -10924,19 +10924,19 @@
         <v>29309</v>
       </c>
       <c r="I138" t="n">
-        <v>13.39</v>
+        <v>13.3907</v>
       </c>
       <c r="J138" t="n">
         <v>23227</v>
       </c>
       <c r="K138" t="n">
-        <v>10.61</v>
+        <v>10.612</v>
       </c>
       <c r="L138" t="n">
-        <v>52.02</v>
+        <v>52.0178</v>
       </c>
       <c r="M138" t="n">
-        <v>56.32</v>
+        <v>56.3206</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>155008</v>
       </c>
       <c r="R138" t="n">
-        <v>79.23</v>
+        <v>79.22799999999999</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -10998,19 +10998,19 @@
         <v>23437</v>
       </c>
       <c r="I139" t="n">
-        <v>12.09</v>
+        <v>12.0897</v>
       </c>
       <c r="J139" t="n">
         <v>16765</v>
       </c>
       <c r="K139" t="n">
-        <v>8.65</v>
+        <v>8.648</v>
       </c>
       <c r="L139" t="n">
-        <v>52.27</v>
+        <v>52.2674</v>
       </c>
       <c r="M139" t="n">
-        <v>54.37</v>
+        <v>54.3713</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>146244</v>
       </c>
       <c r="R139" t="n">
-        <v>82.58</v>
+        <v>82.57989999999999</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -11072,19 +11072,19 @@
         <v>25403</v>
       </c>
       <c r="I140" t="n">
-        <v>11.5</v>
+        <v>11.4985</v>
       </c>
       <c r="J140" t="n">
         <v>19724</v>
       </c>
       <c r="K140" t="n">
-        <v>8.93</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="L140" t="n">
-        <v>51.23</v>
+        <v>51.2289</v>
       </c>
       <c r="M140" t="n">
-        <v>52.44</v>
+        <v>52.4426</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>155237</v>
       </c>
       <c r="R140" t="n">
-        <v>77.16</v>
+        <v>77.15560000000001</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -11146,19 +11146,19 @@
         <v>25428</v>
       </c>
       <c r="I141" t="n">
-        <v>13.58</v>
+        <v>13.5777</v>
       </c>
       <c r="J141" t="n">
         <v>19901</v>
       </c>
       <c r="K141" t="n">
-        <v>10.63</v>
+        <v>10.6264</v>
       </c>
       <c r="L141" t="n">
-        <v>51.52</v>
+        <v>51.5207</v>
       </c>
       <c r="M141" t="n">
-        <v>56.28</v>
+        <v>56.2844</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>133616</v>
       </c>
       <c r="R141" t="n">
-        <v>79.83</v>
+        <v>79.82940000000001</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -11290,16 +11290,16 @@
         <v>2544574</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>14.0049</v>
       </c>
       <c r="H2" t="n">
-        <v>10.33</v>
+        <v>10.3282</v>
       </c>
       <c r="I2" t="n">
-        <v>52.5</v>
+        <v>52.5048</v>
       </c>
       <c r="J2" t="n">
-        <v>53.3</v>
+        <v>53.297</v>
       </c>
     </row>
     <row r="3">
@@ -11324,16 +11324,16 @@
         <v>805427</v>
       </c>
       <c r="G3" t="n">
-        <v>13.17</v>
+        <v>13.1674</v>
       </c>
       <c r="H3" t="n">
-        <v>9.92</v>
+        <v>9.918799999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>50.9</v>
+        <v>50.9006</v>
       </c>
       <c r="J3" t="n">
-        <v>53.56</v>
+        <v>53.5602</v>
       </c>
     </row>
     <row r="4">
@@ -11358,16 +11358,16 @@
         <v>2503848</v>
       </c>
       <c r="G4" t="n">
-        <v>11.65</v>
+        <v>11.6547</v>
       </c>
       <c r="H4" t="n">
-        <v>5.09</v>
+        <v>5.0892</v>
       </c>
       <c r="I4" t="n">
-        <v>51.37</v>
+        <v>51.3653</v>
       </c>
       <c r="J4" t="n">
-        <v>53.18</v>
+        <v>53.1768</v>
       </c>
     </row>
     <row r="5">
@@ -11392,16 +11392,16 @@
         <v>2532715</v>
       </c>
       <c r="G5" t="n">
-        <v>10.18</v>
+        <v>10.1769</v>
       </c>
       <c r="H5" t="n">
-        <v>5.31</v>
+        <v>5.3058</v>
       </c>
       <c r="I5" t="n">
-        <v>52.24</v>
+        <v>52.2353</v>
       </c>
       <c r="J5" t="n">
-        <v>57.63</v>
+        <v>57.6271</v>
       </c>
     </row>
     <row r="6">
@@ -11426,16 +11426,16 @@
         <v>980144</v>
       </c>
       <c r="G6" t="n">
-        <v>9.77</v>
+        <v>9.770899999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>6.87</v>
+        <v>6.8718</v>
       </c>
       <c r="I6" t="n">
-        <v>52.65</v>
+        <v>52.6544</v>
       </c>
       <c r="J6" t="n">
-        <v>56.75</v>
+        <v>56.7476</v>
       </c>
     </row>
     <row r="7">
@@ -11460,16 +11460,16 @@
         <v>1511580</v>
       </c>
       <c r="G7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.703200000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>5.85</v>
+        <v>5.8515</v>
       </c>
       <c r="I7" t="n">
-        <v>51.51</v>
+        <v>51.5097</v>
       </c>
       <c r="J7" t="n">
-        <v>54.31</v>
+        <v>54.3148</v>
       </c>
     </row>
     <row r="8">
@@ -11494,16 +11494,16 @@
         <v>1682697</v>
       </c>
       <c r="G8" t="n">
-        <v>7.84</v>
+        <v>7.8444</v>
       </c>
       <c r="H8" t="n">
-        <v>4.07</v>
+        <v>4.0741</v>
       </c>
       <c r="I8" t="n">
-        <v>52.19</v>
+        <v>52.1892</v>
       </c>
       <c r="J8" t="n">
-        <v>56.65</v>
+        <v>56.6463</v>
       </c>
     </row>
     <row r="9">
@@ -11528,16 +11528,16 @@
         <v>2268721</v>
       </c>
       <c r="G9" t="n">
-        <v>7.81</v>
+        <v>7.8061</v>
       </c>
       <c r="H9" t="n">
-        <v>2.32</v>
+        <v>2.3189</v>
       </c>
       <c r="I9" t="n">
-        <v>51.17</v>
+        <v>51.1746</v>
       </c>
       <c r="J9" t="n">
-        <v>55.7</v>
+        <v>55.7018</v>
       </c>
     </row>
     <row r="10">
@@ -11562,16 +11562,16 @@
         <v>2087992</v>
       </c>
       <c r="G10" t="n">
-        <v>7.31</v>
+        <v>7.3114</v>
       </c>
       <c r="H10" t="n">
-        <v>2.45</v>
+        <v>2.4474</v>
       </c>
       <c r="I10" t="n">
-        <v>52.44</v>
+        <v>52.4376</v>
       </c>
       <c r="J10" t="n">
-        <v>54.38</v>
+        <v>54.3795</v>
       </c>
     </row>
     <row r="11">
@@ -11596,16 +11596,16 @@
         <v>2668817</v>
       </c>
       <c r="G11" t="n">
-        <v>6.96</v>
+        <v>6.9572</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.42</v>
+        <v>-0.4235</v>
       </c>
       <c r="I11" t="n">
-        <v>51.64</v>
+        <v>51.6359</v>
       </c>
       <c r="J11" t="n">
-        <v>56.47</v>
+        <v>56.4727</v>
       </c>
     </row>
     <row r="12">
@@ -11630,16 +11630,16 @@
         <v>643625</v>
       </c>
       <c r="G12" t="n">
-        <v>5.87</v>
+        <v>5.8725</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.22</v>
+        <v>-0.2219</v>
       </c>
       <c r="I12" t="n">
-        <v>51.16</v>
+        <v>51.1554</v>
       </c>
       <c r="J12" t="n">
-        <v>53.22</v>
+        <v>53.2204</v>
       </c>
     </row>
     <row r="13">
@@ -11664,16 +11664,16 @@
         <v>1103618</v>
       </c>
       <c r="G13" t="n">
-        <v>5.14</v>
+        <v>5.1354</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.51</v>
+        <v>-2.5063</v>
       </c>
       <c r="I13" t="n">
-        <v>51.13</v>
+        <v>51.1339</v>
       </c>
       <c r="J13" t="n">
-        <v>58.43</v>
+        <v>58.4348</v>
       </c>
     </row>
     <row r="14">
@@ -11698,16 +11698,16 @@
         <v>3632210</v>
       </c>
       <c r="G14" t="n">
-        <v>4.8</v>
+        <v>4.7956</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.78</v>
+        <v>-6.7802</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>50.0035</v>
       </c>
       <c r="J14" t="n">
-        <v>59.92</v>
+        <v>59.9185</v>
       </c>
     </row>
     <row r="15">
@@ -11732,16 +11732,16 @@
         <v>2176984</v>
       </c>
       <c r="G15" t="n">
-        <v>4.67</v>
+        <v>4.6727</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.01</v>
+        <v>-3.0106</v>
       </c>
       <c r="I15" t="n">
-        <v>52.62</v>
+        <v>52.6231</v>
       </c>
       <c r="J15" t="n">
-        <v>54.27</v>
+        <v>54.2749</v>
       </c>
     </row>
   </sheetData>
